--- a/WorkBot/refactor/data/orders/Performance Food/Performance Food_Downtown_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/Performance Food/Performance Food_Downtown_2025-10-03.xlsx
@@ -770,39 +770,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>CG502</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Monin - Vanilla</t>
+          <t>Spindrift - Lime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>105.63</t>
+          <t>29.96</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CG502</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spindrift - Lime</t>
+          <t>PKT Black Pepper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -812,24 +812,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>31.44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PKT Black Pepper</t>
+          <t>PKT Sugar - (Raw)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -839,24 +839,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>34.14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>34.14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>44256</t>
+          <t>TN374</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PKT Sugar - (Raw)</t>
+          <t>Natalie's - Lemonade</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -866,24 +866,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>9.30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TN374</t>
+          <t>AH252</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Natalie's - Lemonade</t>
+          <t>Natalie's - Orange Juice</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -893,24 +893,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>24.50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AH252</t>
+          <t>TN454</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Natalie's - Orange Juice</t>
+          <t>Natalie's - Orange Mango</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -920,24 +920,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>13.38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TN454</t>
+          <t>TN362</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Natalie's - Orange Mango</t>
+          <t>Natalie's - Orange Pineapple</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,12 +959,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TN362</t>
+          <t>TN380</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Natalie's - Orange Pineapple</t>
+          <t>Natalie's - Strawberry Lemonade</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -974,39 +974,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>10.15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TN380</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Natalie's - Strawberry Lemonade</t>
+          <t>Monin - Vanilla</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>105.63</t>
         </is>
       </c>
     </row>
